--- a/data/analisis/concentracion_2026-10-26.xlsx
+++ b/data/analisis/concentracion_2026-10-26.xlsx
@@ -469,7 +469,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26 13:22</t>
+          <t>2026-10-26 15:38</t>
         </is>
       </c>
       <c r="B2" t="n">
